--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA9A9C42-F369-4013-B333-3C58114A9A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{705AFF26-FBE4-4D86-A40C-80703AE0BD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{705AFF26-FBE4-4D86-A40C-80703AE0BD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22EBC6AF-8AAE-4DD4-9617-C0F31D6EE1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22EBC6AF-8AAE-4DD4-9617-C0F31D6EE1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AAD0989-13B3-4801-BF49-7CA943EDC43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AAD0989-13B3-4801-BF49-7CA943EDC43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34A30D2-786F-42F7-983F-1029895F0818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34A30D2-786F-42F7-983F-1029895F0818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7BD2A98-074B-4B1F-B4BF-784B6363B814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7BD2A98-074B-4B1F-B4BF-784B6363B814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2858ED78-FCF5-4AAF-8CB1-7D686855FBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2858ED78-FCF5-4AAF-8CB1-7D686855FBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4B6A629-7F98-406F-8A5D-AA89F6A183F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4B6A629-7F98-406F-8A5D-AA89F6A183F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A6B9AA6-3196-47AB-9FEE-0823D233F60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A6B9AA6-3196-47AB-9FEE-0823D233F60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5060CFD6-D575-4BF1-97EA-CC6170776E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5060CFD6-D575-4BF1-97EA-CC6170776E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24B1DDC1-C668-4995-9D48-839418895543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24B1DDC1-C668-4995-9D48-839418895543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68296D0B-283D-468F-8E2B-645975B244BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68296D0B-283D-468F-8E2B-645975B244BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ABBDEA7-8C03-4E18-8EF2-92FFC0A9C0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ABBDEA7-8C03-4E18-8EF2-92FFC0A9C0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B72DBAF5-5E7C-40DA-AC2E-9F2D36A29D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B72DBAF5-5E7C-40DA-AC2E-9F2D36A29D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7392CE5-E34B-4924-A3E1-5F4E2515F65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7392CE5-E34B-4924-A3E1-5F4E2515F65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACBECA5B-FD00-470D-9D2C-55701B7D10E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="191">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -298,6 +298,12 @@
     <t>at grid node - r17609399-220</t>
   </si>
   <si>
+    <t>w94053861-220</t>
+  </si>
+  <si>
+    <t>at grid node - w94053861-220</t>
+  </si>
+  <si>
     <t>NZ12-220</t>
   </si>
   <si>
@@ -343,6 +349,12 @@
     <t>at grid node - NZ11-220</t>
   </si>
   <si>
+    <t>w180514007-220</t>
+  </si>
+  <si>
+    <t>at grid node - w180514007-220</t>
+  </si>
+  <si>
     <t>w412589726-220</t>
   </si>
   <si>
@@ -391,12 +403,6 @@
     <t>at grid node - NZ22-220</t>
   </si>
   <si>
-    <t>w180514007-220</t>
-  </si>
-  <si>
-    <t>at grid node - w180514007-220</t>
-  </si>
-  <si>
     <t>NZ30-220</t>
   </si>
   <si>
@@ -442,6 +448,48 @@
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
+    <t>w1026587442-220</t>
+  </si>
+  <si>
+    <t>at grid node - w1026587442-220</t>
+  </si>
+  <si>
+    <t>w167572576-220</t>
+  </si>
+  <si>
+    <t>at grid node - w167572576-220</t>
+  </si>
+  <si>
+    <t>NZ42-220</t>
+  </si>
+  <si>
+    <t>at grid node - NZ42-220</t>
+  </si>
+  <si>
+    <t>NZ23-220</t>
+  </si>
+  <si>
+    <t>at grid node - NZ23-220</t>
+  </si>
+  <si>
+    <t>w414953388-220</t>
+  </si>
+  <si>
+    <t>at grid node - w414953388-220</t>
+  </si>
+  <si>
+    <t>w89636510-220</t>
+  </si>
+  <si>
+    <t>at grid node - w89636510-220</t>
+  </si>
+  <si>
+    <t>NZ31-220</t>
+  </si>
+  <si>
+    <t>at grid node - NZ31-220</t>
+  </si>
+  <si>
     <t>w148300699-220</t>
   </si>
   <si>
@@ -484,6 +532,12 @@
     <t>at grid node - NZ16-220</t>
   </si>
   <si>
+    <t>w270022030-220</t>
+  </si>
+  <si>
+    <t>at grid node - w270022030-220</t>
+  </si>
+  <si>
     <t>NZ17-220</t>
   </si>
   <si>
@@ -502,6 +556,12 @@
     <t>at grid node - w167285260-220</t>
   </si>
   <si>
+    <t>w94840399-220</t>
+  </si>
+  <si>
+    <t>at grid node - w94840399-220</t>
+  </si>
+  <si>
     <t>w93713118-220</t>
   </si>
   <si>
@@ -509,12 +569,6 @@
   </si>
   <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>w94053861-220</t>
-  </si>
-  <si>
-    <t>at grid node - w94053861-220</t>
   </si>
   <si>
     <t>w95343089-220</t>
@@ -884,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T46"/>
+  <dimension ref="B3:T56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:20" x14ac:dyDescent="0.45">
@@ -989,13 +1043,13 @@
         <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L11" t="s">
         <v>78</v>
@@ -1007,19 +1061,19 @@
         <v>80</v>
       </c>
       <c r="O11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q11" t="s">
         <v>78</v>
       </c>
       <c r="R11" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="S11" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="T11" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -1039,13 +1093,13 @@
         <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" t="s">
         <v>90</v>
-      </c>
-      <c r="J12" t="s">
-        <v>88</v>
       </c>
       <c r="L12" t="s">
         <v>78</v>
@@ -1057,19 +1111,19 @@
         <v>83</v>
       </c>
       <c r="O12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q12" t="s">
         <v>78</v>
       </c>
       <c r="R12" t="s">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="S12" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="T12" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -1089,13 +1143,13 @@
         <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s">
         <v>78</v>
@@ -1107,57 +1161,69 @@
         <v>85</v>
       </c>
       <c r="O13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
       </c>
       <c r="R13" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="S13" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="T13" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
       <c r="G14" t="s">
         <v>78</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L14" t="s">
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="N14" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q14" t="s">
         <v>78</v>
       </c>
       <c r="R14" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="S14" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="T14" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -1165,13 +1231,13 @@
         <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L15" t="s">
         <v>78</v>
@@ -1183,19 +1249,19 @@
         <v>137</v>
       </c>
       <c r="O15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q15" t="s">
         <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="S15" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="T15" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -1203,13 +1269,13 @@
         <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s">
         <v>78</v>
@@ -1221,19 +1287,19 @@
         <v>139</v>
       </c>
       <c r="O16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q16" t="s">
         <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="S16" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="T16" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="7:20" x14ac:dyDescent="0.45">
@@ -1241,13 +1307,13 @@
         <v>78</v>
       </c>
       <c r="H17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s">
         <v>78</v>
@@ -1259,19 +1325,19 @@
         <v>141</v>
       </c>
       <c r="O17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q17" t="s">
         <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S17" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="T17" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="7:20" x14ac:dyDescent="0.45">
@@ -1279,13 +1345,13 @@
         <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s">
         <v>78</v>
@@ -1297,19 +1363,19 @@
         <v>143</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q18" t="s">
         <v>78</v>
       </c>
       <c r="R18" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="S18" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="T18" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="7:20" x14ac:dyDescent="0.45">
@@ -1317,37 +1383,37 @@
         <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s">
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="N19" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q19" t="s">
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="S19" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="T19" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="7:20" x14ac:dyDescent="0.45">
@@ -1355,25 +1421,25 @@
         <v>78</v>
       </c>
       <c r="H20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s">
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q20" t="s">
         <v>78</v>
@@ -1385,7 +1451,7 @@
         <v>85</v>
       </c>
       <c r="T20" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="7:20" x14ac:dyDescent="0.45">
@@ -1393,25 +1459,25 @@
         <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s">
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="7:20" x14ac:dyDescent="0.45">
@@ -1419,25 +1485,25 @@
         <v>78</v>
       </c>
       <c r="H22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L22" t="s">
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="7:20" x14ac:dyDescent="0.45">
@@ -1445,25 +1511,25 @@
         <v>78</v>
       </c>
       <c r="H23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s">
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O23" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="7:20" x14ac:dyDescent="0.45">
@@ -1471,25 +1537,25 @@
         <v>78</v>
       </c>
       <c r="H24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L24" t="s">
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="N24" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="O24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="7:20" x14ac:dyDescent="0.45">
@@ -1497,25 +1563,25 @@
         <v>78</v>
       </c>
       <c r="H25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L25" t="s">
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="N25" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="O25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="7:20" x14ac:dyDescent="0.45">
@@ -1523,25 +1589,25 @@
         <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s">
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="N26" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="O26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="7:20" x14ac:dyDescent="0.45">
@@ -1549,25 +1615,25 @@
         <v>78</v>
       </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s">
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="N27" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="O27" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="7:20" x14ac:dyDescent="0.45">
@@ -1575,25 +1641,25 @@
         <v>78</v>
       </c>
       <c r="H28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L28" t="s">
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="N28" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="O28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="7:20" x14ac:dyDescent="0.45">
@@ -1601,25 +1667,25 @@
         <v>78</v>
       </c>
       <c r="H29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L29" t="s">
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="N29" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="O29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="7:20" x14ac:dyDescent="0.45">
@@ -1627,25 +1693,25 @@
         <v>78</v>
       </c>
       <c r="H30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s">
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="N30" t="s">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="O30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="7:20" x14ac:dyDescent="0.45">
@@ -1653,25 +1719,25 @@
         <v>78</v>
       </c>
       <c r="H31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I31" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s">
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="N31" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="O31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="7:20" x14ac:dyDescent="0.45">
@@ -1679,25 +1745,25 @@
         <v>78</v>
       </c>
       <c r="H32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L32" t="s">
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="N32" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="O32" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.45">
@@ -1705,25 +1771,25 @@
         <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J33" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L33" t="s">
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="N33" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="O33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="7:15" x14ac:dyDescent="0.45">
@@ -1731,13 +1797,13 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="N34" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="O34" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.45">
@@ -1745,13 +1811,13 @@
         <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="N35" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="O35" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="7:15" x14ac:dyDescent="0.45">
@@ -1759,13 +1825,13 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="N36" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="O36" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="7:15" x14ac:dyDescent="0.45">
@@ -1773,13 +1839,13 @@
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="N37" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="O37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="7:15" x14ac:dyDescent="0.45">
@@ -1787,13 +1853,13 @@
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="N38" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="O38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="7:15" x14ac:dyDescent="0.45">
@@ -1801,13 +1867,13 @@
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="N39" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="O39" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="7:15" x14ac:dyDescent="0.45">
@@ -1815,13 +1881,13 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="N40" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="O40" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="7:15" x14ac:dyDescent="0.45">
@@ -1829,13 +1895,13 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="N41" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="O41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="7:15" x14ac:dyDescent="0.45">
@@ -1843,13 +1909,13 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="N42" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="O42" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="7:15" x14ac:dyDescent="0.45">
@@ -1857,13 +1923,13 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="N43" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="O43" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="7:15" x14ac:dyDescent="0.45">
@@ -1871,13 +1937,13 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="N44" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="O44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="7:15" x14ac:dyDescent="0.45">
@@ -1885,13 +1951,13 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="N45" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="O45" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="7:15" x14ac:dyDescent="0.45">
@@ -1899,13 +1965,153 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
+        <v>113</v>
+      </c>
+      <c r="N46" t="s">
+        <v>114</v>
+      </c>
+      <c r="O46" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M47" t="s">
+        <v>115</v>
+      </c>
+      <c r="N47" t="s">
+        <v>116</v>
+      </c>
+      <c r="O47" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L48" t="s">
+        <v>78</v>
+      </c>
+      <c r="M48" t="s">
+        <v>119</v>
+      </c>
+      <c r="N48" t="s">
+        <v>120</v>
+      </c>
+      <c r="O48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L49" t="s">
+        <v>78</v>
+      </c>
+      <c r="M49" t="s">
+        <v>121</v>
+      </c>
+      <c r="N49" t="s">
+        <v>122</v>
+      </c>
+      <c r="O49" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>78</v>
+      </c>
+      <c r="M50" t="s">
+        <v>123</v>
+      </c>
+      <c r="N50" t="s">
+        <v>124</v>
+      </c>
+      <c r="O50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M51" t="s">
+        <v>125</v>
+      </c>
+      <c r="N51" t="s">
+        <v>126</v>
+      </c>
+      <c r="O51" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L52" t="s">
+        <v>78</v>
+      </c>
+      <c r="M52" t="s">
+        <v>127</v>
+      </c>
+      <c r="N52" t="s">
+        <v>128</v>
+      </c>
+      <c r="O52" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L53" t="s">
+        <v>78</v>
+      </c>
+      <c r="M53" t="s">
+        <v>129</v>
+      </c>
+      <c r="N53" t="s">
+        <v>130</v>
+      </c>
+      <c r="O53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L54" t="s">
+        <v>78</v>
+      </c>
+      <c r="M54" t="s">
         <v>131</v>
       </c>
-      <c r="N46" t="s">
+      <c r="N54" t="s">
         <v>132</v>
       </c>
-      <c r="O46" t="s">
+      <c r="O54" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>78</v>
+      </c>
+      <c r="M55" t="s">
         <v>133</v>
+      </c>
+      <c r="N55" t="s">
+        <v>134</v>
+      </c>
+      <c r="O55" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L56" t="s">
+        <v>78</v>
+      </c>
+      <c r="M56" t="s">
+        <v>172</v>
+      </c>
+      <c r="N56" t="s">
+        <v>173</v>
+      </c>
+      <c r="O56" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NZL_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACBECA5B-FD00-470D-9D2C-55701B7D10E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57724A4C-C638-4F94-8414-429DDBD0BB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
